--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-v3RoleCode-cs.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/CodeSystem-jp-v3RoleCode-cs.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>http://terminology.ht7.org/Codesystem/v3-RoleCode where concept is-a FAMMEB の日本語補足</t>
+    <t>http://terminology.hl7.org/Codesystem/v3-RoleCode where concept is-a FAMMEB の日本語補足</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -120,7 +120,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.ht7.org/Codesystem/v3-RoleCode</t>
+    <t>http://terminology.hl7.org/Codesystem/v3-RoleCode</t>
   </si>
   <si>
     <t>Count</t>
